--- a/data/trans_bre/IP19C03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 17,23</t>
+          <t>-12,19; 15,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 6,97</t>
+          <t>-25,45; 6,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 14,59</t>
+          <t>-27,95; 16,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 38,18</t>
+          <t>-10,69; 36,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,8; 118,56</t>
+          <t>-39,47; 101,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-59,82; 29,22</t>
+          <t>-59,66; 25,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,11; 60,93</t>
+          <t>-60,25; 67,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-61,1; 952,91</t>
+          <t>-63,37; 725,62</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 12,97</t>
+          <t>0,74; 12,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 7,99</t>
+          <t>-4,7; 7,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 6,24</t>
+          <t>-5,46; 6,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 5,73</t>
+          <t>-6,18; 5,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 90,2</t>
+          <t>3,16; 86,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 47,35</t>
+          <t>-20,67; 42,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 40,4</t>
+          <t>-25,78; 41,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 39,33</t>
+          <t>-28,34; 40,02</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 1,46</t>
+          <t>-16,66; 1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 15,87</t>
+          <t>-1,47; 15,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 3,85</t>
+          <t>-11,06; 3,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 11,94</t>
+          <t>-5,44; 10,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,61; 17,13</t>
+          <t>-72,08; 18,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 369,76</t>
+          <t>-17,81; 356,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,56; 59,75</t>
+          <t>-70,54; 49,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-36,09; 143,2</t>
+          <t>-33,36; 129,11</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 7,87</t>
+          <t>-1,19; 8,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 6,02</t>
+          <t>-3,85; 6,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 3,43</t>
+          <t>-6,27; 3,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 6,07</t>
+          <t>-3,22; 6,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 51,36</t>
+          <t>-5,77; 55,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 36,2</t>
+          <t>-17,58; 36,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 22,16</t>
+          <t>-29,57; 19,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 43,57</t>
+          <t>-17,46; 46,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 15,64</t>
+          <t>-13,32; 17,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 6,07</t>
+          <t>-25,45; 6,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 16,28</t>
+          <t>-29,69; 12,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 36,77</t>
+          <t>-10,44; 36,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 101,67</t>
+          <t>-45,19; 129,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 25,89</t>
+          <t>-58,61; 26,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,25; 67,92</t>
+          <t>-64,54; 52,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-63,37; 725,62</t>
+          <t>-64,06; 897,07</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 12,5</t>
+          <t>0,93; 12,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 7,63</t>
+          <t>-4,49; 8,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 6,31</t>
+          <t>-5,85; 6,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 5,8</t>
+          <t>-6,25; 5,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 86,04</t>
+          <t>4,76; 86,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 42,09</t>
+          <t>-18,69; 44,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,78; 41,21</t>
+          <t>-25,9; 40,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,34; 40,02</t>
+          <t>-29,8; 36,36</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 1,32</t>
+          <t>-16,75; 1,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 15,12</t>
+          <t>-0,96; 15,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 3,33</t>
+          <t>-11,65; 3,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 10,71</t>
+          <t>-5,02; 11,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-72,08; 18,11</t>
+          <t>-72,73; 17,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 356,64</t>
+          <t>-10,58; 397,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,54; 49,48</t>
+          <t>-73,39; 44,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 129,11</t>
+          <t>-32,67; 132,81</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 8,08</t>
+          <t>-1,11; 8,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 6,07</t>
+          <t>-3,58; 5,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 3,18</t>
+          <t>-5,9; 3,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 6,53</t>
+          <t>-3,75; 6,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 55,01</t>
+          <t>-5,84; 53,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 36,25</t>
+          <t>-15,87; 33,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 19,71</t>
+          <t>-28,37; 19,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 46,99</t>
+          <t>-19,62; 43,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,85</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 17,36</t>
+          <t>-11,84; 17,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 6,2</t>
+          <t>-25,17; 6,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-29,69; 12,21</t>
+          <t>-28,06; 14,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 36,81</t>
+          <t>-18,08; 18,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 129,78</t>
+          <t>-41,8; 118,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,61; 26,13</t>
+          <t>-59,82; 29,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,54; 52,51</t>
+          <t>-64,11; 60,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-64,06; 897,07</t>
+          <t>-69,22; 410,04</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-2,16%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 12,57</t>
+          <t>0,96; 12,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 8,01</t>
+          <t>-4,77; 7,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 6,35</t>
+          <t>-5,13; 6,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 5,53</t>
+          <t>-5,93; 6,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 86,56</t>
+          <t>3,79; 90,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 44,75</t>
+          <t>-19,45; 47,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 40,33</t>
+          <t>-24,14; 40,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 36,36</t>
+          <t>-28,44; 43,05</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>3,94</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 1,2</t>
+          <t>-15,64; 1,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 15,49</t>
+          <t>0,1; 15,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 3,52</t>
+          <t>-10,31; 3,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 11,24</t>
+          <t>-4,31; 12,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-72,73; 17,73</t>
+          <t>-73,61; 17,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 397,31</t>
+          <t>-7,01; 369,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-73,39; 44,96</t>
+          <t>-70,56; 59,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 132,81</t>
+          <t>-30,24; 160,23</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 8,28</t>
+          <t>-1,56; 7,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 5,76</t>
+          <t>-3,68; 6,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 3,11</t>
+          <t>-5,63; 3,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 6,28</t>
+          <t>-3,43; 5,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 53,74</t>
+          <t>-8,24; 51,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 33,59</t>
+          <t>-16,24; 36,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 19,42</t>
+          <t>-26,95; 22,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 43,85</t>
+          <t>-19,66; 40,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C03-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-9,69</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-8,64</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-28,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-23,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.717518907099656</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-9.694484889078675</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-8.635339242154316</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.6686048640154596</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1235961714395813</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.2810983538788054</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.2336921498889077</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.04147031640038084</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-11,84; 17,23</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-25,17; 6,97</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-28,06; 14,59</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-18,08; 18,96</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-41,8; 118,56</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-59,82; 29,22</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-64,11; 60,93</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-69,22; 410,04</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-11.84082175596854</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-25.17104660464634</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-28.05927073528914</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-18.08421778751366</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4180141221217383</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5981900094334719</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.6411310692308335</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.692162431900104</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>17.2314298162976</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.970308053651743</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>14.58695904603419</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>18.96185139682738</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.185643952535536</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2921601025545819</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.6093417189457365</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>4.10036441056676</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,63</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,37</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>38,97%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,96; 12,97</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,77; 7,99</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,13; 6,24</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,93; 6,17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3,79; 90,2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-19,45; 47,35</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-24,14; 40,4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-28,44; 43,05</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>6.626918998395342</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.372481001214437</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.7615138763304552</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.04667126264014665</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3897453108302109</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.06635823452560818</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.04142825882305466</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.002627725679761445</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-7,2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,06</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,68</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,94</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-42,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-31,61%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>35,91%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.9566380089844643</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.773908267000459</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.129335761241232</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.934866341521507</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.03792700195362309</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1944757842455666</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.241356733153557</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2843640682166784</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-15,64; 1,46</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 15,87</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-10,31; 3,85</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,31; 12,44</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-73,61; 17,13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-7,01; 369,76</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-70,56; 59,75</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-30,24; 160,23</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>12.96539096517569</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.985161067596446</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.239008015238479</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>6.166232265329471</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.9020018993947901</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.4735441921761275</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.4039742657988913</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.4304832363209296</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-6,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-7.19651950742239</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7.064880240700649</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.67668467344443</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3.943916935432429</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.4292041027663337</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.9242641233870046</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.3160819244594276</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.3591269093190047</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,56; 7,87</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,68; 6,02</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,63; 3,43</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,43; 5,54</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-8,24; 51,36</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-16,24; 36,2</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-26,95; 22,16</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-19,66; 40,05</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-15.64281908272087</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.1006641094014163</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-10.31390173492049</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.308135402957962</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.736134967409555</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.07005004865685671</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7055840102578292</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3023770135675142</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.457307419454139</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>15.86974715218155</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.846830153925959</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>12.43525988086795</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1713419081616842</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>3.697592531397581</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.59749267914477</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.60226482150562</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>3.195259145257123</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.242244785383304</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.197430948146572</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.182347233879991</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1821031286744006</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.06402929473860157</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.06581632759428456</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.07481427292244748</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.563120393880569</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.677277002867448</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.628604645530022</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.430634351798952</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.08241125215799043</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1624184683845573</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2694787922735372</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1966384700889748</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.866137563631765</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.019567994140757</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.433660951318086</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.537416335800693</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5135953675968137</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3620196931720713</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.221639448007089</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.4004741970520224</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
